--- a/MEME_OUTPUT/reverse_meme_out_4_motif4.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_4_motif4.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TAGA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TCTA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AGAT</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.0352</v>
+        <v>0.0353858456617353</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.9994</v>
+        <v>0.9992003198720512</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="5">
@@ -564,16 +564,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G5" t="n">
-        <v>0.9966</v>
+        <v>0.9964014394242303</v>
       </c>
     </row>
     <row r="6">
@@ -598,11 +598,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8838</v>
+        <v>0.8836465413834467</v>
       </c>
     </row>
     <row r="7">
@@ -622,16 +622,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.981</v>
+        <v>0.9808076769292283</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/reverse_meme_out_4_motif4.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_4_motif4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TAGACGCGGCATTCTA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TAGA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TCTA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;CGCGGCAT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.0353858456617353</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AATTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9992003198720512</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AATTTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>AATTTTAGACGCGGCATT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TTTTAGACGCGGCA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9964014394242303</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>CGCGGCATTCTAGCG</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>CG</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;CGGCATTCTAG&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.8836465413834467</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TCTAGCGA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;TAGC&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9808076769292283</v>
       </c>
     </row>
